--- a/virtual-physics-lab/app/dl/HCI_Q1_springs.xlsx
+++ b/virtual-physics-lab/app/dl/HCI_Q1_springs.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +102,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -692,91 +695,91 @@
       <c r="A6" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>13.8</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>15.6</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>8.4</v>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>17.5</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>19.3</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>10.2</v>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>20.7</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>11.1</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>450</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>12.5</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -874,25 +877,25 @@
       <c r="A6" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>13.8</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>(B6-2*3.8)/100</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>(C6-3.8)/100</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>D6^2/4+E6^2</f>
         <v/>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <f>(A6/1000)^2</f>
         <v/>
       </c>
@@ -901,7 +904,7 @@
           <t>gradient</t>
         </is>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="8">
         <f>SLOPE(F6:F11,G6:G11)</f>
         <v/>
       </c>
@@ -915,25 +918,25 @@
       <c r="A7" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>15.6</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>8.4</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>(B7-2*3.8)/100</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>(C7-3.8)/100</f>
         <v/>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <f>D7^2/4+E7^2</f>
         <v/>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <f>(A7/1000)^2</f>
         <v/>
       </c>
@@ -942,7 +945,7 @@
           <t>y-intercept</t>
         </is>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="8">
         <f>INTERCEPT(F6:F11,G6:G11)</f>
         <v/>
       </c>
@@ -956,25 +959,25 @@
       <c r="A8" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>17.5</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>(B8-2*3.8)/100</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>(C8-3.8)/100</f>
         <v/>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f>D8^2/4+E8^2</f>
         <v/>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <f>(A8/1000)^2</f>
         <v/>
       </c>
@@ -983,7 +986,7 @@
           <t>k = g/√gradient</t>
         </is>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="8">
         <f>9.81/SQRT(SLOPE(F6:F11,G6:G11))</f>
         <v/>
       </c>
@@ -997,25 +1000,25 @@
       <c r="A9" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>19.3</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>10.2</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>(B9-2*3.8)/100</f>
         <v/>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f>(C9-3.8)/100</f>
         <v/>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <f>D9^2/4+E9^2</f>
         <v/>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <f>(A9/1000)^2</f>
         <v/>
       </c>
@@ -1024,25 +1027,25 @@
       <c r="A10" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>20.7</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>11.1</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>(B10-2*3.8)/100</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>(C10-3.8)/100</f>
         <v/>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <f>D10^2/4+E10^2</f>
         <v/>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <f>(A10/1000)^2</f>
         <v/>
       </c>
@@ -1051,25 +1054,25 @@
       <c r="A11" s="5" t="n">
         <v>450</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>12.5</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>(B11-2*3.8)/100</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>(C11-3.8)/100</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f>D11^2/4+E11^2</f>
         <v/>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <f>(A11/1000)^2</f>
         <v/>
       </c>
